--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Hyperglycemia monitoring/check observations aligned with build_observation_hyperglycemia_measurement_checks().</t>
+    <t>Observation profile for hyperglycemia monitoring, checks and measured values.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -715,7 +715,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -792,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Registry observation concept</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -836,10 +836,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -890,10 +890,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1009,7 +1009,7 @@
 booleaninteger</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Hyperglycemia indicator or measured value</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1794,98 +1794,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2079,10 +2081,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2164,7 +2166,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/hyperglycemia-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/hyperglycemia-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -807,7 +807,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/analitics-codes-vs</t>
+    <t>http://qualityregistry.org/ValueSet/analitics-codes-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -832,7 +832,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -886,7 +886,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hyperglycemia-observation-profile.xlsx
+++ b/StructureDefinition-hyperglycemia-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
